--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484330_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484330_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2137</v>
+        <v>4.4908</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8518</v>
+        <v>3.9928</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3619</v>
+        <v>0.498</v>
       </c>
       <c r="G2" t="n">
         <v>2.3764</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.974</v>
+        <v>1.2512</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2396</v>
+        <v>0.3806</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.8706</v>
       </c>
       <c r="V2" t="n">
         <v>0.2772</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7873</v>
+        <v>3.6012</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5614</v>
+        <v>1.4779</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2259</v>
+        <v>2.1233</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6125</v>
+        <v>5.5614</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1789</v>
+        <v>3.9292</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5663</v>
+        <v>1.6322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5639</v>
+        <v>5.8618</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8035</v>
+        <v>3.419</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2396</v>
+        <v>2.4427</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0486</v>
+        <v>-0.3003</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3753</v>
+        <v>0.5102</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6733</v>
+        <v>-0.8105</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>0.9113</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7789</v>
+        <v>-0.1449</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5011</v>
+        <v>1.0562</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6549</v>
+        <v>3.4111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9325</v>
+        <v>1.9946</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7224</v>
+        <v>1.4166</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5614</v>
+        <v>1.6125</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9292</v>
+        <v>2.1789</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6322</v>
+        <v>-0.5663</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8618</v>
+        <v>0.5639</v>
       </c>
       <c r="K4" t="n">
-        <v>3.419</v>
+        <v>1.8035</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4427</v>
+        <v>-1.2396</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3003</v>
+        <v>1.0486</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5102</v>
+        <v>0.3753</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8105</v>
+        <v>0.6733</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.965</v>
+        <v>0.9038</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6904</v>
+        <v>0.212</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6554</v>
+        <v>0.6917</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0459</v>
+        <v>2.6457</v>
       </c>
       <c r="E5" t="n">
-        <v>1.964</v>
+        <v>1.7817</v>
       </c>
       <c r="F5" t="n">
-        <v>1.082</v>
+        <v>0.8641</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0435</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5853</v>
+        <v>1.1851</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4817</v>
+        <v>0.2994</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1036</v>
+        <v>0.8857</v>
       </c>
       <c r="V5" t="n">
         <v>0.3321</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3889</v>
+        <v>2.5621</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0644</v>
+        <v>2.4283</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3245</v>
+        <v>0.1338</v>
       </c>
       <c r="G6" t="n">
         <v>1.52</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2828</v>
+        <v>0.456</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.2841</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3625</v>
+        <v>0.1719</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1564</v>
+        <v>0.4287</v>
       </c>
       <c r="E7" t="n">
         <v>-1.206</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3623</v>
+        <v>1.6347</v>
       </c>
       <c r="G7" t="n">
         <v>2.1098</v>
@@ -1000,13 +1000,13 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.586</v>
+        <v>-0.3137</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0935</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4925</v>
+        <v>-0.2202</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.4246</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="F8" t="n">
         <v>-0.4047</v>
@@ -1078,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9301</v>
+        <v>-0.9157</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2391</v>
+        <v>-2.3609</v>
       </c>
       <c r="F9" t="n">
-        <v>1.309</v>
+        <v>1.4452</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4392</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.077</v>
+        <v>-0.0626</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0689</v>
+        <v>-0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1459</v>
+        <v>-0.0097</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0314</v>
+        <v>-1.4981</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1921</v>
+        <v>-2.7677</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1607</v>
+        <v>1.2696</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7366</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3181</v>
+        <v>0.2153</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3218</v>
+        <v>0.1026</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0038</v>
+        <v>0.1127</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1979</v>
+        <v>-2.5289</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8262</v>
+        <v>-2.3206</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3717</v>
+        <v>-0.2083</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3477</v>
@@ -1312,13 +1312,13 @@
         <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1469</v>
+        <v>0.5221</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5777</v>
+        <v>-0.0721</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4308</v>
+        <v>0.5942</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5545</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.562</v>
+        <v>11.7723</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7897</v>
+        <v>3.0002</v>
       </c>
       <c r="F12" t="n">
         <v>8.7723</v>
@@ -1360,7 +1360,7 @@
         <v>10.8827</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6741999999999999</v>
+        <v>-0.6741999999999995</v>
       </c>
       <c r="J12" t="n">
         <v>10.0373</v>
@@ -1369,13 +1369,13 @@
         <v>7.332800000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>2.7044</v>
+        <v>2.704400000000001</v>
       </c>
       <c r="M12" t="n">
         <v>0.1712999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>3.549700000000001</v>
+        <v>3.5497</v>
       </c>
       <c r="O12" t="n">
         <v>-3.3784</v>
@@ -1387,16 +1387,16 @@
         <v>-12.6973</v>
       </c>
       <c r="R12" t="n">
-        <v>9.767300000000001</v>
+        <v>9.767299999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8381</v>
+        <v>5.0486</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3149999999999999</v>
+        <v>0.8954</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1532</v>
+        <v>4.1531</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5545</v>
@@ -1405,7 +1405,7 @@
         <v>4.764699999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.3194</v>
+        <v>-5.319399999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5166</v>
+        <v>3.5434</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9488</v>
+        <v>3.3532</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4321</v>
+        <v>0.1902</v>
       </c>
       <c r="G13" t="n">
         <v>-0.14</v>
@@ -1468,13 +1468,13 @@
         <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5853</v>
+        <v>-0.5585</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2626</v>
+        <v>-0.8582</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3227</v>
+        <v>0.2997</v>
       </c>
       <c r="V13" t="n">
         <v>3.6559</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0427</v>
+        <v>1.3123</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7016</v>
+        <v>0.8984</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3411</v>
+        <v>0.4139</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1328</v>
+        <v>-1.4957</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0376</v>
+        <v>-2.2103</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0951</v>
+        <v>0.7146</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3036</v>
+        <v>0.4316</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3441</v>
+        <v>-0.9581</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>1.3897</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-1.9273</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6935</v>
+        <v>-1.2522</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1356</v>
+        <v>-0.6751</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>2.222</v>
+        <v>-0.2153</v>
       </c>
       <c r="T14" t="n">
-        <v>1.728</v>
+        <v>-0.7984</v>
       </c>
       <c r="U14" t="n">
-        <v>0.494</v>
+        <v>0.5831</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6093</v>
+        <v>2.4373</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4604</v>
+        <v>0.6516</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7973</v>
+        <v>0.286</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6631</v>
+        <v>0.3656</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4957</v>
+        <v>-1.1328</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2103</v>
+        <v>-1.0376</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7146</v>
+        <v>-0.0951</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4316</v>
+        <v>-0.3036</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9581</v>
+        <v>-0.3441</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3897</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9273</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2522</v>
+        <v>-0.6935</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6751</v>
+        <v>-0.1356</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0672</v>
+        <v>0.8309</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8995</v>
+        <v>0.3124</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8323</v>
+        <v>0.5185</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4373</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4373</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4009</v>
+        <v>-0.0047</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5943000000000001</v>
+        <v>0.3157</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8065</v>
+        <v>-0.3204</v>
       </c>
       <c r="G16" t="n">
         <v>0.0858</v>
@@ -1702,13 +1702,13 @@
         <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.522</v>
+        <v>-0.1258</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5131</v>
+        <v>-0.603</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.4772</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9414</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7716</v>
+        <v>-2.0573</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4276</v>
+        <v>-2.2254</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.344</v>
+        <v>0.1681</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3547</v>
@@ -1780,13 +1780,13 @@
         <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3388</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2626</v>
+        <v>-1.0604</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0762</v>
+        <v>0.4359</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2735</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2629</v>
+        <v>-2.536</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.798</v>
+        <v>-2.4576</v>
       </c>
       <c r="F18" t="n">
-        <v>0.535</v>
+        <v>-0.0784</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7282</v>
+        <v>-1.2915</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.119</v>
+        <v>-0.1855</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3908</v>
+        <v>-1.106</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5737</v>
+        <v>-0.4619</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.6951</v>
+        <v>0.1036</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>-0.5655</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1544</v>
+        <v>-0.8295</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4239</v>
+        <v>-0.2891</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2694</v>
+        <v>-0.5405</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3285</v>
+        <v>-0.1664</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0522</v>
+        <v>-0.3548</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3807</v>
+        <v>0.1883</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>-1.2735</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.349</v>
+        <v>-3.7297</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4576</v>
+        <v>-4.1013</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8914</v>
+        <v>0.3716</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2915</v>
+        <v>-2.7282</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1855</v>
+        <v>-3.119</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.106</v>
+        <v>0.3908</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4619</v>
+        <v>-2.5737</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1036</v>
+        <v>-2.6951</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5655</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8295</v>
+        <v>-0.1544</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2891</v>
+        <v>-0.4239</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5405</v>
+        <v>0.2694</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9794</v>
+        <v>-0.1383</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3548</v>
+        <v>-0.3555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6246</v>
+        <v>0.2173</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2735</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.7972</v>
+        <v>-5.0451</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.9425</v>
+        <v>-4.8413</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8547</v>
+        <v>-0.2038</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1516</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.1437</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5364</v>
+        <v>-0.4352</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3594</v>
+        <v>0.2916</v>
       </c>
       <c r="V20" t="n">
         <v>-1.1638</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.5619</v>
+        <v>-7.865499999999998</v>
       </c>
       <c r="E21" t="n">
         <v>-8.772300000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7895</v>
+        <v>0.9067999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-10.2087</v>
@@ -2062,7 +2062,7 @@
         <v>-10.8827</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6741000000000004</v>
+        <v>0.6741000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>-0.1713000000000005</v>
@@ -2083,7 +2083,7 @@
         <v>-2.7044</v>
       </c>
       <c r="P21" t="n">
-        <v>2.93</v>
+        <v>2.930000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-9.767299999999999</v>
@@ -2092,19 +2092,19 @@
         <v>12.6973</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.8379</v>
+        <v>-1.1416</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.1532</v>
+        <v>-4.1531</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3151</v>
+        <v>3.0116</v>
       </c>
       <c r="V21" t="n">
         <v>0.5544999999999995</v>
       </c>
       <c r="W21" t="n">
-        <v>5.3192</v>
+        <v>5.319199999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-4.764699999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484330_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484330_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4908</v>
+        <v>3.6012</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9928</v>
+        <v>1.4779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.498</v>
+        <v>2.1233</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3764</v>
+        <v>5.5614</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2161</v>
+        <v>3.9292</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1603</v>
+        <v>1.6322</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0112</v>
+        <v>5.8618</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1754</v>
+        <v>3.419</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8358</v>
+        <v>2.4427</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6348</v>
+        <v>-0.3003</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0407</v>
+        <v>0.5102</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6755</v>
+        <v>-0.8105</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1721</v>
+        <v>-3.9069</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2512</v>
+        <v>0.9113</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3806</v>
+        <v>-0.1449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8706</v>
+        <v>1.0562</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7731</v>
+        <v>-0.3321</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6012</v>
+        <v>3.4111</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4779</v>
+        <v>1.9946</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1233</v>
+        <v>1.4166</v>
       </c>
       <c r="G3" t="n">
-        <v>5.5614</v>
+        <v>1.6125</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9292</v>
+        <v>2.1789</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6322</v>
+        <v>-0.5663</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8618</v>
+        <v>0.5639</v>
       </c>
       <c r="K3" t="n">
-        <v>3.419</v>
+        <v>1.8035</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4427</v>
+        <v>-1.2396</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3003</v>
+        <v>1.0486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5102</v>
+        <v>0.3753</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8105</v>
+        <v>0.6733</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9113</v>
+        <v>0.9038</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1449</v>
+        <v>0.212</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0562</v>
+        <v>0.6917</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +736,72 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4111</v>
+        <v>3.3489</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9946</v>
+        <v>3.3489</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4166</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6125</v>
+        <v>3.3489</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1789</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5663</v>
+        <v>2.4279</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5639</v>
+        <v>3.3489</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8035</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2396</v>
+        <v>2.4279</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0486</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3753</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6733</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9038</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6917</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4287</v>
+        <v>1.1419</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.206</v>
+        <v>0.6439</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6347</v>
+        <v>0.498</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1098</v>
+        <v>-0.9725</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3277</v>
+        <v>0.2952</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7821</v>
+        <v>-1.2677</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0363</v>
+        <v>-0.3377</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3888</v>
+        <v>0.2545</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6475</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0735</v>
+        <v>-0.6348</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9389</v>
+        <v>0.0407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1346</v>
+        <v>-0.6755</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3137</v>
+        <v>1.2512</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0935</v>
+        <v>0.3806</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2202</v>
+        <v>0.8706</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4246</v>
+        <v>0.4287</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0199</v>
+        <v>-1.206</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4047</v>
+        <v>1.6347</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4047</v>
+        <v>2.1098</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.3277</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4047</v>
+        <v>0.7821</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.0363</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.3888</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6475</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4047</v>
+        <v>1.0735</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.9389</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4047</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0199</v>
+        <v>-0.3137</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0199</v>
+        <v>-0.0935</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.2202</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,6 +1129,11 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9157</v>
+        <v>0.307</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3609</v>
+        <v>0.307</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4452</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4392</v>
+        <v>0.307</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4009</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0383</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.308</v>
+        <v>0.307</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0003</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8688</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5994</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0626</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4981</v>
+        <v>-0.4246</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7677</v>
+        <v>-0.0199</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2696</v>
+        <v>-0.4047</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7366</v>
+        <v>-0.4047</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2218</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4852</v>
+        <v>-0.4047</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9401</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.021</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2035</v>
+        <v>-0.4047</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7992</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4043</v>
+        <v>-0.4047</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2153</v>
+        <v>-0.0199</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1026</v>
+        <v>-0.0199</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1127</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5289</v>
+        <v>-1.2227</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3206</v>
+        <v>-2.6679</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2083</v>
+        <v>1.4452</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3477</v>
+        <v>-1.7462</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7247</v>
+        <v>-0.7079</v>
       </c>
       <c r="I11" t="n">
-        <v>0.377</v>
+        <v>-1.0383</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6816</v>
+        <v>-2.615</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7752</v>
+        <v>-1.3073</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4568</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0293</v>
+        <v>0.8688</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0504</v>
+        <v>0.5994</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0797</v>
+        <v>0.2694</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5221</v>
+        <v>-0.0626</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0721</v>
+        <v>-0.0529</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5942</v>
+        <v>-0.0097</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,229 +1400,240 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.7723</v>
+        <v>-1.4981</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0002</v>
+        <v>-2.7677</v>
       </c>
       <c r="F12" t="n">
-        <v>8.7723</v>
+        <v>1.2696</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2084</v>
+        <v>-0.7366</v>
       </c>
       <c r="H12" t="n">
-        <v>10.8827</v>
+        <v>-1.2218</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6741999999999995</v>
+        <v>0.4852</v>
       </c>
       <c r="J12" t="n">
-        <v>10.0373</v>
+        <v>-1.9401</v>
       </c>
       <c r="K12" t="n">
-        <v>7.332800000000001</v>
+        <v>-2.021</v>
       </c>
       <c r="L12" t="n">
-        <v>2.704400000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1712999999999998</v>
+        <v>1.2035</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5497</v>
+        <v>0.7992</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.3784</v>
+        <v>0.4043</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9302</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6973</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>9.767299999999999</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0486</v>
+        <v>0.2153</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8954</v>
+        <v>0.1026</v>
       </c>
       <c r="U12" t="n">
-        <v>4.1531</v>
+        <v>0.1127</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.764699999999999</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.319399999999999</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5434</v>
+        <v>-2.5289</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3532</v>
+        <v>-2.3206</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1902</v>
+        <v>-0.2083</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.14</v>
+        <v>-0.3477</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.7247</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6881</v>
+        <v>0.377</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7276</v>
+        <v>0.6816</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4988</v>
+        <v>-0.7752</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2288</v>
+        <v>1.4568</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8676</v>
+        <v>-1.0293</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3269</v>
+        <v>0.0504</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5407</v>
+        <v>-1.0797</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5585</v>
+        <v>0.5221</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8582</v>
+        <v>-0.0721</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2997</v>
+        <v>0.5942</v>
       </c>
       <c r="V13" t="n">
-        <v>3.6559</v>
+        <v>-0.5545</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3123</v>
+        <v>11.7723</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8984</v>
+        <v>3.000200000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4139</v>
+        <v>8.772300000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4957</v>
+        <v>10.2084</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2103</v>
+        <v>10.8828</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7146</v>
+        <v>-0.6742999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4316</v>
+        <v>10.0373</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9581</v>
+        <v>7.3329</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3897</v>
+        <v>2.7043</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9273</v>
+        <v>0.1712999999999996</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2522</v>
+        <v>3.5497</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6751</v>
+        <v>-3.3784</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-2.9302</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-12.6973</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>9.767300000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2153</v>
+        <v>5.048600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7984</v>
+        <v>0.8954</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5831</v>
+        <v>4.153099999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>-0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.319399999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6516</v>
+        <v>3.5434</v>
       </c>
       <c r="E15" t="n">
-        <v>0.286</v>
+        <v>3.3532</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3656</v>
+        <v>0.1902</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1328</v>
+        <v>-0.14</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0376</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0951</v>
+        <v>0.6881</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3036</v>
+        <v>1.7276</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3441</v>
+        <v>0.4988</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>1.2288</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-1.8676</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6935</v>
+        <v>-1.3269</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1356</v>
+        <v>-0.5407</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8309</v>
+        <v>-0.5585</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3124</v>
+        <v>-0.8582</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5185</v>
+        <v>0.2997</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6093</v>
+        <v>3.6559</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>3.6559</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0047</v>
+        <v>1.3123</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3157</v>
+        <v>0.8984</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3204</v>
+        <v>0.4139</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0858</v>
+        <v>-1.4957</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1842</v>
+        <v>-2.2103</v>
       </c>
       <c r="I16" t="n">
-        <v>0.27</v>
+        <v>0.7146</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8135</v>
+        <v>0.4316</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2727</v>
+        <v>-0.9581</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5409</v>
+        <v>1.3897</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7277</v>
+        <v>-1.9273</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4569</v>
+        <v>-1.2522</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2708</v>
+        <v>-0.6751</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1258</v>
+        <v>-0.2153</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.603</v>
+        <v>-0.7984</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4772</v>
+        <v>0.5831</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9414</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0573</v>
+        <v>0.6516</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2254</v>
+        <v>0.286</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1681</v>
+        <v>0.3656</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3547</v>
+        <v>-1.1328</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1622</v>
+        <v>-1.0376</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8075</v>
+        <v>-0.0951</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6479</v>
+        <v>-0.3036</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8353</v>
+        <v>-0.3441</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4832</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0026</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3269</v>
+        <v>-0.6935</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6757</v>
+        <v>-0.1356</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6245000000000001</v>
+        <v>0.8309</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0604</v>
+        <v>0.3124</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4359</v>
+        <v>0.5185</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2735</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.536</v>
+        <v>-0.0047</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4576</v>
+        <v>0.3157</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0784</v>
+        <v>-0.3204</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2915</v>
+        <v>0.0858</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1855</v>
+        <v>-0.1842</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.106</v>
+        <v>0.27</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4619</v>
+        <v>1.8135</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1036</v>
+        <v>1.2727</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5655</v>
+        <v>0.5409</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8295</v>
+        <v>-1.7277</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2891</v>
+        <v>-1.4569</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5405</v>
+        <v>-0.2708</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1664</v>
+        <v>-0.1258</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3548</v>
+        <v>-0.603</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1883</v>
+        <v>0.4772</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2735</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7297</v>
+        <v>-2.0573</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.1013</v>
+        <v>-2.2254</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3716</v>
+        <v>0.1681</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7282</v>
+        <v>-0.3547</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.119</v>
+        <v>-2.1622</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3908</v>
+        <v>1.8075</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5737</v>
+        <v>1.6479</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6951</v>
+        <v>-0.8353</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1214</v>
+        <v>2.4832</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1544</v>
+        <v>-2.0026</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4239</v>
+        <v>-1.3269</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2694</v>
+        <v>-0.6757</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1383</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3555</v>
+        <v>-1.0604</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2173</v>
+        <v>0.4359</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>-1.2735</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0451</v>
+        <v>-2.536</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8413</v>
+        <v>-2.4576</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2038</v>
+        <v>-0.0784</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1516</v>
+        <v>-1.2915</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1558</v>
+        <v>-0.1855</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9958</v>
+        <v>-1.106</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4527</v>
+        <v>-0.4619</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.1036</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8604</v>
+        <v>-0.5655</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.699</v>
+        <v>-0.8295</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5636</v>
+        <v>-0.2891</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.5405</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1437</v>
+        <v>-0.1664</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4352</v>
+        <v>-0.3548</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2916</v>
+        <v>0.1883</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1638</v>
+        <v>-1.2735</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1638</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,235 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-3.7297</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.1013</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-2.7282</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-3.119</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.5737</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-2.6951</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.1544</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.4239</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.1383</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.3555</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L. ANDUJAR MASCARO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.0451</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-4.8413</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.2038</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.1516</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.1558</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.9958</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2.4527</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.5921999999999999</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.8604</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.699</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.5636</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1437</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.4352</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484330_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>-7.865499999999998</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>-8.772300000000001</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>0.9067999999999999</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G23" t="n">
         <v>-10.2087</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H23" t="n">
         <v>-10.8827</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>0.6741000000000001</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>-0.1713000000000005</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K23" t="n">
         <v>-3.5497</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>3.3786</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M23" t="n">
         <v>-10.0372</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N23" t="n">
         <v>-7.333</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>-2.7044</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>2.930000000000001</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q23" t="n">
         <v>-9.767299999999999</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R23" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>-1.1416</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>-4.1531</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>3.0116</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V23" t="n">
         <v>0.5544999999999995</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>5.319199999999999</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-4.764699999999999</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
